--- a/selenium-tests/reports/selenium-test-report.xlsx
+++ b/selenium-tests/reports/selenium-test-report.xlsx
@@ -430,10 +430,10 @@
         <v>PASS</v>
       </c>
       <c r="D2" t="str">
-        <v>4.36 sec</v>
+        <v>2.17 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-29T12:43:00.621Z</v>
+        <v>2026-07-29T12:52:45.615Z</v>
       </c>
       <c r="F2" t="str">
         <v>Success</v>
@@ -450,10 +450,10 @@
         <v>PASS</v>
       </c>
       <c r="D3" t="str">
-        <v>2.18 sec</v>
+        <v>2.15 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-29T12:43:02.807Z</v>
+        <v>2026-07-29T12:52:47.765Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -470,10 +470,10 @@
         <v>PASS</v>
       </c>
       <c r="D4" t="str">
-        <v>2.51 sec</v>
+        <v>2.14 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-29T12:43:05.313Z</v>
+        <v>2026-07-29T12:52:49.902Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -490,10 +490,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>2.22 sec</v>
+        <v>2.31 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-29T12:43:07.529Z</v>
+        <v>2026-07-29T12:52:52.214Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -510,16 +510,16 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>1.39 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-29T12:43:08.918Z</v>
+        <v>2026-07-29T12:52:53.555Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
+    <row r="7">
       <c r="A7" t="str">
         <v>TC006</v>
       </c>
@@ -527,17 +527,16 @@
         <v>Registration page can be reached</v>
       </c>
       <c r="C7" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>11.39 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-29T12:43:20.309Z</v>
-      </c>
-      <c r="F7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Waiting for element to be located By(xpath, //button[contains(text(), 'Create Account')])
-Wait timed out after 10080ms</v>
+        <v>2026-07-29T12:52:55.010Z</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Success</v>
       </c>
     </row>
     <row r="8">
@@ -554,7 +553,7 @@
         <v>1.53 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-29T12:43:21.844Z</v>
+        <v>2026-07-29T12:52:56.541Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -571,10 +570,10 @@
         <v>PASS</v>
       </c>
       <c r="D9" t="str">
-        <v>1.42 sec</v>
+        <v>1.50 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-29T12:43:23.259Z</v>
+        <v>2026-07-29T12:52:58.037Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>

--- a/selenium-tests/reports/selenium-test-report.xlsx
+++ b/selenium-tests/reports/selenium-test-report.xlsx
@@ -430,10 +430,10 @@
         <v>PASS</v>
       </c>
       <c r="D2" t="str">
-        <v>2.17 sec</v>
+        <v>3.19 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-29T12:52:45.615Z</v>
+        <v>2026-07-29T13:04:35.218Z</v>
       </c>
       <c r="F2" t="str">
         <v>Success</v>
@@ -450,10 +450,10 @@
         <v>PASS</v>
       </c>
       <c r="D3" t="str">
-        <v>2.15 sec</v>
+        <v>2.45 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-29T12:52:47.765Z</v>
+        <v>2026-07-29T13:04:37.675Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -470,10 +470,10 @@
         <v>PASS</v>
       </c>
       <c r="D4" t="str">
-        <v>2.14 sec</v>
+        <v>2.28 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-29T12:52:49.902Z</v>
+        <v>2026-07-29T13:04:39.958Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -490,10 +490,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>2.31 sec</v>
+        <v>2.25 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-29T12:52:52.214Z</v>
+        <v>2026-07-29T13:04:42.203Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -510,10 +510,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>1.34 sec</v>
+        <v>1.42 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-29T12:52:53.555Z</v>
+        <v>2026-07-29T13:04:43.620Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -530,10 +530,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>1.45 sec</v>
+        <v>1.36 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-29T12:52:55.010Z</v>
+        <v>2026-07-29T13:04:44.976Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -550,10 +550,10 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>1.53 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-29T12:52:56.541Z</v>
+        <v>2026-07-29T13:04:46.326Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -570,10 +570,10 @@
         <v>PASS</v>
       </c>
       <c r="D9" t="str">
-        <v>1.50 sec</v>
+        <v>1.41 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-29T12:52:58.037Z</v>
+        <v>2026-07-29T13:04:47.733Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>

--- a/selenium-tests/reports/selenium-test-report.xlsx
+++ b/selenium-tests/reports/selenium-test-report.xlsx
@@ -430,10 +430,10 @@
         <v>PASS</v>
       </c>
       <c r="D2" t="str">
-        <v>3.19 sec</v>
+        <v>2.22 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-29T13:04:35.218Z</v>
+        <v>2026-07-29T14:08:47.125Z</v>
       </c>
       <c r="F2" t="str">
         <v>Success</v>
@@ -450,10 +450,10 @@
         <v>PASS</v>
       </c>
       <c r="D3" t="str">
-        <v>2.45 sec</v>
+        <v>2.04 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-29T13:04:37.675Z</v>
+        <v>2026-07-29T14:08:49.163Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -470,10 +470,10 @@
         <v>PASS</v>
       </c>
       <c r="D4" t="str">
-        <v>2.28 sec</v>
+        <v>2.13 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-29T13:04:39.958Z</v>
+        <v>2026-07-29T14:08:51.291Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -490,10 +490,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>2.25 sec</v>
+        <v>2.31 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-29T13:04:42.203Z</v>
+        <v>2026-07-29T14:08:53.597Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -510,10 +510,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>1.42 sec</v>
+        <v>1.36 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-29T13:04:43.620Z</v>
+        <v>2026-07-29T14:08:54.953Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -530,10 +530,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>1.36 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-29T13:04:44.976Z</v>
+        <v>2026-07-29T14:08:56.280Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -550,10 +550,10 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>1.35 sec</v>
+        <v>1.64 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-29T13:04:46.326Z</v>
+        <v>2026-07-29T14:08:57.916Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -570,10 +570,10 @@
         <v>PASS</v>
       </c>
       <c r="D9" t="str">
-        <v>1.41 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-29T13:04:47.733Z</v>
+        <v>2026-07-29T14:08:59.353Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>

--- a/selenium-tests/reports/selenium-test-report.xlsx
+++ b/selenium-tests/reports/selenium-test-report.xlsx
@@ -430,10 +430,10 @@
         <v>PASS</v>
       </c>
       <c r="D2" t="str">
-        <v>2.22 sec</v>
+        <v>2.20 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-29T14:08:47.125Z</v>
+        <v>2026-07-29T14:21:13.893Z</v>
       </c>
       <c r="F2" t="str">
         <v>Success</v>
@@ -450,10 +450,10 @@
         <v>PASS</v>
       </c>
       <c r="D3" t="str">
-        <v>2.04 sec</v>
+        <v>2.33 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-29T14:08:49.163Z</v>
+        <v>2026-07-29T14:21:16.225Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -470,10 +470,10 @@
         <v>PASS</v>
       </c>
       <c r="D4" t="str">
-        <v>2.13 sec</v>
+        <v>2.14 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-29T14:08:51.291Z</v>
+        <v>2026-07-29T14:21:18.363Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -490,10 +490,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>2.31 sec</v>
+        <v>2.27 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-29T14:08:53.597Z</v>
+        <v>2026-07-29T14:21:20.635Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -510,10 +510,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>1.36 sec</v>
+        <v>1.39 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-29T14:08:54.953Z</v>
+        <v>2026-07-29T14:21:22.024Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -530,10 +530,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>1.33 sec</v>
+        <v>1.43 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-29T14:08:56.280Z</v>
+        <v>2026-07-29T14:21:23.453Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -550,10 +550,10 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>1.64 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-29T14:08:57.916Z</v>
+        <v>2026-07-29T14:21:24.806Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -570,10 +570,10 @@
         <v>PASS</v>
       </c>
       <c r="D9" t="str">
-        <v>1.44 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-29T14:08:59.353Z</v>
+        <v>2026-07-29T14:21:26.128Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>

--- a/selenium-tests/reports/selenium-test-report.xlsx
+++ b/selenium-tests/reports/selenium-test-report.xlsx
@@ -430,10 +430,10 @@
         <v>PASS</v>
       </c>
       <c r="D2" t="str">
-        <v>4.33 sec</v>
+        <v>2.50 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F2" t="str" xml:space="preserve">
         <v xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
@@ -454,7 +454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -474,7 +474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -494,7 +494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -514,7 +514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -534,7 +534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -554,7 +554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -574,7 +574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -594,7 +594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -614,7 +614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F11" t="str">
         <v>Success</v>
@@ -634,7 +634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F12" t="str">
         <v>Success</v>
@@ -654,7 +654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F13" t="str">
         <v>Success</v>
@@ -674,7 +674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F14" t="str">
         <v>Success</v>
@@ -694,7 +694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F15" t="str">
         <v>Success</v>
@@ -714,7 +714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F16" t="str">
         <v>Success</v>
@@ -734,7 +734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F17" t="str">
         <v>Success</v>
@@ -754,7 +754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F18" t="str">
         <v>Success</v>
@@ -774,7 +774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F19" t="str">
         <v>Success</v>
@@ -794,7 +794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F20" t="str">
         <v>Success</v>
@@ -814,7 +814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F21" t="str">
         <v>Success</v>
@@ -834,7 +834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F22" t="str">
         <v>Success</v>
@@ -854,7 +854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F23" t="str">
         <v>Success</v>
@@ -874,7 +874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F24" t="str">
         <v>Success</v>
@@ -894,7 +894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F25" t="str">
         <v>Success</v>
@@ -914,7 +914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F26" t="str">
         <v>Success</v>
@@ -934,7 +934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F27" t="str">
         <v>Success</v>
@@ -954,7 +954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F28" t="str">
         <v>Success</v>
@@ -974,7 +974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F29" t="str">
         <v>Success</v>
@@ -994,7 +994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F30" t="str">
         <v>Success</v>
@@ -1014,7 +1014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F31" t="str">
         <v>Success</v>
@@ -1034,7 +1034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F32" t="str">
         <v>Success</v>
@@ -1054,7 +1054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F33" t="str">
         <v>Success</v>
@@ -1074,7 +1074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F34" t="str">
         <v>Success</v>
@@ -1094,7 +1094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F35" t="str">
         <v>Success</v>
@@ -1114,7 +1114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F36" t="str">
         <v>Success</v>
@@ -1134,7 +1134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F37" t="str">
         <v>Success</v>
@@ -1154,7 +1154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F38" t="str">
         <v>Success</v>
@@ -1174,7 +1174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F39" t="str">
         <v>Success</v>
@@ -1194,7 +1194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F40" t="str">
         <v>Success</v>
@@ -1214,7 +1214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F41" t="str">
         <v>Success</v>
@@ -1234,7 +1234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F42" t="str">
         <v>Success</v>
@@ -1254,7 +1254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F43" t="str">
         <v>Success</v>
@@ -1274,7 +1274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F44" t="str">
         <v>Success</v>
@@ -1294,7 +1294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F45" t="str">
         <v>Success</v>
@@ -1314,7 +1314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F46" t="str">
         <v>Success</v>
@@ -1334,7 +1334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F47" t="str">
         <v>Success</v>
@@ -1354,7 +1354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F48" t="str">
         <v>Success</v>
@@ -1374,7 +1374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F49" t="str">
         <v>Success</v>
@@ -1394,7 +1394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F50" t="str">
         <v>Success</v>
@@ -1414,7 +1414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F51" t="str">
         <v>Success</v>
@@ -1434,7 +1434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F52" t="str">
         <v>Success</v>
@@ -1454,7 +1454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F53" t="str">
         <v>Success</v>
@@ -1474,7 +1474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F54" t="str">
         <v>Success</v>
@@ -1494,7 +1494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F55" t="str">
         <v>Success</v>
@@ -1514,7 +1514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F56" t="str">
         <v>Success</v>
@@ -1534,7 +1534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F57" t="str">
         <v>Success</v>
@@ -1554,7 +1554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F58" t="str">
         <v>Success</v>
@@ -1574,7 +1574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F59" t="str">
         <v>Success</v>
@@ -1594,7 +1594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F60" t="str">
         <v>Success</v>
@@ -1614,7 +1614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F61" t="str">
         <v>Success</v>
@@ -1634,7 +1634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F62" t="str">
         <v>Success</v>
@@ -1654,7 +1654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F63" t="str">
         <v>Success</v>
@@ -1674,7 +1674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F64" t="str">
         <v>Success</v>
@@ -1694,7 +1694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F65" t="str">
         <v>Success</v>
@@ -1714,7 +1714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F66" t="str">
         <v>Success</v>
@@ -1734,7 +1734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F67" t="str">
         <v>Success</v>
@@ -1754,7 +1754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F68" t="str">
         <v>Success</v>
@@ -1774,7 +1774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F69" t="str">
         <v>Success</v>
@@ -1794,7 +1794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F70" t="str">
         <v>Success</v>
@@ -1814,7 +1814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F71" t="str">
         <v>Success</v>
@@ -1834,7 +1834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F72" t="str">
         <v>Success</v>
@@ -1854,7 +1854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F73" t="str">
         <v>Success</v>
@@ -1874,7 +1874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F74" t="str">
         <v>Success</v>
@@ -1894,7 +1894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F75" t="str">
         <v>Success</v>
@@ -1914,7 +1914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F76" t="str">
         <v>Success</v>
@@ -1934,7 +1934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F77" t="str">
         <v>Success</v>
@@ -1954,7 +1954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F78" t="str">
         <v>Success</v>
@@ -1974,7 +1974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F79" t="str">
         <v>Success</v>
@@ -1994,7 +1994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F80" t="str">
         <v>Success</v>
@@ -2014,7 +2014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F81" t="str">
         <v>Success</v>
@@ -2034,7 +2034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F82" t="str">
         <v>Success</v>
@@ -2054,7 +2054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F83" t="str">
         <v>Success</v>
@@ -2074,7 +2074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F84" t="str">
         <v>Success</v>
@@ -2094,7 +2094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F85" t="str">
         <v>Success</v>
@@ -2114,7 +2114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F86" t="str">
         <v>Success</v>
@@ -2134,7 +2134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F87" t="str">
         <v>Success</v>
@@ -2154,7 +2154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F88" t="str">
         <v>Success</v>
@@ -2174,7 +2174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F89" t="str">
         <v>Success</v>
@@ -2194,7 +2194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F90" t="str">
         <v>Success</v>
@@ -2214,7 +2214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F91" t="str">
         <v>Success</v>
@@ -2234,7 +2234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F92" t="str">
         <v>Success</v>
@@ -2254,7 +2254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F93" t="str">
         <v>Success</v>
@@ -2274,7 +2274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F94" t="str">
         <v>Success</v>
@@ -2294,7 +2294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F95" t="str">
         <v>Success</v>
@@ -2314,7 +2314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F96" t="str">
         <v>Success</v>
@@ -2334,7 +2334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F97" t="str">
         <v>Success</v>
@@ -2354,7 +2354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F98" t="str">
         <v>Success</v>
@@ -2374,7 +2374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F99" t="str">
         <v>Success</v>
@@ -2394,7 +2394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F100" t="str">
         <v>Success</v>
@@ -2414,7 +2414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F101" t="str">
         <v>Success</v>
@@ -2434,7 +2434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F102" t="str">
         <v>Success</v>
@@ -2454,7 +2454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F103" t="str">
         <v>Success</v>
@@ -2474,7 +2474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F104" t="str">
         <v>Success</v>
@@ -2494,7 +2494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F105" t="str">
         <v>Success</v>
@@ -2514,7 +2514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F106" t="str">
         <v>Success</v>
@@ -2534,7 +2534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F107" t="str">
         <v>Success</v>
@@ -2554,7 +2554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F108" t="str">
         <v>Success</v>
@@ -2574,7 +2574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F109" t="str">
         <v>Success</v>
@@ -2594,7 +2594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F110" t="str">
         <v>Success</v>
@@ -2614,7 +2614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F111" t="str">
         <v>Success</v>
@@ -2634,7 +2634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F112" t="str">
         <v>Success</v>
@@ -2654,7 +2654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F113" t="str">
         <v>Success</v>
@@ -2674,7 +2674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F114" t="str">
         <v>Success</v>
@@ -2694,7 +2694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F115" t="str">
         <v>Success</v>
@@ -2714,7 +2714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F116" t="str">
         <v>Success</v>
@@ -2734,7 +2734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F117" t="str">
         <v>Success</v>
@@ -2754,7 +2754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F118" t="str">
         <v>Success</v>
@@ -2774,7 +2774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F119" t="str">
         <v>Success</v>
@@ -2794,7 +2794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F120" t="str">
         <v>Success</v>
@@ -2814,7 +2814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F121" t="str">
         <v>Success</v>
@@ -2834,7 +2834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F122" t="str">
         <v>Success</v>
@@ -2854,7 +2854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F123" t="str">
         <v>Success</v>
@@ -2874,7 +2874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F124" t="str">
         <v>Success</v>
@@ -2894,7 +2894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F125" t="str">
         <v>Success</v>
@@ -2914,7 +2914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F126" t="str">
         <v>Success</v>
@@ -2934,7 +2934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F127" t="str">
         <v>Success</v>
@@ -2954,7 +2954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F128" t="str">
         <v>Success</v>
@@ -2974,7 +2974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F129" t="str">
         <v>Success</v>
@@ -2994,7 +2994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F130" t="str">
         <v>Success</v>
@@ -3014,7 +3014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F131" t="str">
         <v>Success</v>
@@ -3034,7 +3034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F132" t="str">
         <v>Success</v>
@@ -3054,7 +3054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F133" t="str">
         <v>Success</v>
@@ -3074,7 +3074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F134" t="str">
         <v>Success</v>
@@ -3094,7 +3094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F135" t="str">
         <v>Success</v>
@@ -3114,7 +3114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F136" t="str">
         <v>Success</v>
@@ -3134,7 +3134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F137" t="str">
         <v>Success</v>
@@ -3154,7 +3154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F138" t="str">
         <v>Success</v>
@@ -3174,7 +3174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F139" t="str">
         <v>Success</v>
@@ -3194,7 +3194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F140" t="str">
         <v>Success</v>
@@ -3214,7 +3214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F141" t="str">
         <v>Success</v>
@@ -3234,7 +3234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F142" t="str">
         <v>Success</v>
@@ -3254,7 +3254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F143" t="str">
         <v>Success</v>
@@ -3274,7 +3274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F144" t="str">
         <v>Success</v>
@@ -3294,7 +3294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F145" t="str">
         <v>Success</v>
@@ -3314,7 +3314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F146" t="str">
         <v>Success</v>
@@ -3334,7 +3334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F147" t="str">
         <v>Success</v>
@@ -3354,7 +3354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F148" t="str">
         <v>Success</v>
@@ -3374,7 +3374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F149" t="str">
         <v>Success</v>
@@ -3394,7 +3394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F150" t="str">
         <v>Success</v>
@@ -3414,7 +3414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F151" t="str">
         <v>Success</v>
@@ -3434,7 +3434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F152" t="str">
         <v>Success</v>
@@ -3454,7 +3454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F153" t="str">
         <v>Success</v>
@@ -3474,7 +3474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F154" t="str">
         <v>Success</v>
@@ -3494,7 +3494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F155" t="str">
         <v>Success</v>
@@ -3514,7 +3514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F156" t="str">
         <v>Success</v>
@@ -3534,7 +3534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F157" t="str">
         <v>Success</v>
@@ -3554,7 +3554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F158" t="str">
         <v>Success</v>
@@ -3574,7 +3574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F159" t="str">
         <v>Success</v>
@@ -3594,7 +3594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F160" t="str">
         <v>Success</v>
@@ -3614,7 +3614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F161" t="str">
         <v>Success</v>
@@ -3634,7 +3634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F162" t="str">
         <v>Success</v>
@@ -3654,7 +3654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F163" t="str">
         <v>Success</v>
@@ -3674,7 +3674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F164" t="str">
         <v>Success</v>
@@ -3694,7 +3694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F165" t="str">
         <v>Success</v>
@@ -3714,7 +3714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F166" t="str">
         <v>Success</v>
@@ -3734,7 +3734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F167" t="str">
         <v>Success</v>
@@ -3754,7 +3754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F168" t="str">
         <v>Success</v>
@@ -3774,7 +3774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F169" t="str">
         <v>Success</v>
@@ -3794,7 +3794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F170" t="str">
         <v>Success</v>
@@ -3814,7 +3814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F171" t="str">
         <v>Success</v>
@@ -3834,7 +3834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F172" t="str">
         <v>Success</v>
@@ -3854,7 +3854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F173" t="str">
         <v>Success</v>
@@ -3874,7 +3874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F174" t="str">
         <v>Success</v>
@@ -3894,7 +3894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F175" t="str">
         <v>Success</v>
@@ -3914,7 +3914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F176" t="str">
         <v>Success</v>
@@ -3934,7 +3934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F177" t="str">
         <v>Success</v>
@@ -3954,7 +3954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F178" t="str">
         <v>Success</v>
@@ -3974,7 +3974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F179" t="str">
         <v>Success</v>
@@ -3994,7 +3994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F180" t="str">
         <v>Success</v>
@@ -4014,7 +4014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F181" t="str">
         <v>Success</v>
@@ -4034,7 +4034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F182" t="str">
         <v>Success</v>
@@ -4054,7 +4054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F183" t="str">
         <v>Success</v>
@@ -4074,7 +4074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F184" t="str">
         <v>Success</v>
@@ -4094,7 +4094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F185" t="str">
         <v>Success</v>
@@ -4114,7 +4114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F186" t="str">
         <v>Success</v>
@@ -4134,7 +4134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F187" t="str">
         <v>Success</v>
@@ -4154,7 +4154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F188" t="str">
         <v>Success</v>
@@ -4174,7 +4174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F189" t="str">
         <v>Success</v>
@@ -4194,7 +4194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F190" t="str">
         <v>Success</v>
@@ -4214,7 +4214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F191" t="str">
         <v>Success</v>
@@ -4234,7 +4234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F192" t="str">
         <v>Success</v>
@@ -4254,7 +4254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F193" t="str">
         <v>Success</v>
@@ -4274,7 +4274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F194" t="str">
         <v>Success</v>
@@ -4294,7 +4294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F195" t="str">
         <v>Success</v>
@@ -4314,7 +4314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F196" t="str">
         <v>Success</v>
@@ -4334,7 +4334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F197" t="str">
         <v>Success</v>
@@ -4354,7 +4354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F198" t="str">
         <v>Success</v>
@@ -4374,7 +4374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F199" t="str">
         <v>Success</v>
@@ -4394,7 +4394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F200" t="str">
         <v>Success</v>
@@ -4414,7 +4414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F201" t="str">
         <v>Success</v>
@@ -4434,7 +4434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F202" t="str">
         <v>Success</v>
@@ -4454,7 +4454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F203" t="str">
         <v>Success</v>
@@ -4474,7 +4474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F204" t="str">
         <v>Success</v>
@@ -4494,7 +4494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F205" t="str">
         <v>Success</v>
@@ -4514,7 +4514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F206" t="str">
         <v>Success</v>
@@ -4534,7 +4534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F207" t="str">
         <v>Success</v>
@@ -4554,7 +4554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F208" t="str">
         <v>Success</v>
@@ -4574,7 +4574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F209" t="str">
         <v>Success</v>
@@ -4594,7 +4594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F210" t="str">
         <v>Success</v>
@@ -4614,7 +4614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F211" t="str">
         <v>Success</v>
@@ -4634,7 +4634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F212" t="str">
         <v>Success</v>
@@ -4654,7 +4654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F213" t="str">
         <v>Success</v>
@@ -4674,7 +4674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F214" t="str">
         <v>Success</v>
@@ -4694,7 +4694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F215" t="str">
         <v>Success</v>
@@ -4714,7 +4714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F216" t="str">
         <v>Success</v>
@@ -4734,7 +4734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F217" t="str">
         <v>Success</v>
@@ -4754,7 +4754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F218" t="str">
         <v>Success</v>
@@ -4774,7 +4774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F219" t="str">
         <v>Success</v>
@@ -4794,7 +4794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F220" t="str">
         <v>Success</v>
@@ -4814,7 +4814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F221" t="str">
         <v>Success</v>
@@ -4834,7 +4834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F222" t="str">
         <v>Success</v>
@@ -4854,7 +4854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F223" t="str">
         <v>Success</v>
@@ -4874,7 +4874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F224" t="str">
         <v>Success</v>
@@ -4894,7 +4894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F225" t="str">
         <v>Success</v>
@@ -4914,7 +4914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F226" t="str">
         <v>Success</v>
@@ -4934,7 +4934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F227" t="str">
         <v>Success</v>
@@ -4954,7 +4954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F228" t="str">
         <v>Success</v>
@@ -4974,7 +4974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F229" t="str">
         <v>Success</v>
@@ -4994,7 +4994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F230" t="str">
         <v>Success</v>
@@ -5014,7 +5014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F231" t="str">
         <v>Success</v>
@@ -5034,7 +5034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F232" t="str">
         <v>Success</v>
@@ -5054,7 +5054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F233" t="str">
         <v>Success</v>
@@ -5074,7 +5074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F234" t="str">
         <v>Success</v>
@@ -5094,7 +5094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F235" t="str">
         <v>Success</v>
@@ -5114,7 +5114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F236" t="str">
         <v>Success</v>
@@ -5134,7 +5134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F237" t="str">
         <v>Success</v>
@@ -5154,7 +5154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F238" t="str">
         <v>Success</v>
@@ -5174,7 +5174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F239" t="str">
         <v>Success</v>
@@ -5194,7 +5194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F240" t="str">
         <v>Success</v>
@@ -5214,7 +5214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F241" t="str">
         <v>Success</v>
@@ -5234,7 +5234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F242" t="str">
         <v>Success</v>
@@ -5254,7 +5254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F243" t="str">
         <v>Success</v>
@@ -5274,7 +5274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F244" t="str">
         <v>Success</v>
@@ -5294,7 +5294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F245" t="str">
         <v>Success</v>
@@ -5314,7 +5314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F246" t="str">
         <v>Success</v>
@@ -5334,7 +5334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F247" t="str">
         <v>Success</v>
@@ -5354,7 +5354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F248" t="str">
         <v>Success</v>
@@ -5374,7 +5374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F249" t="str">
         <v>Success</v>
@@ -5394,7 +5394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F250" t="str">
         <v>Success</v>
@@ -5414,7 +5414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F251" t="str">
         <v>Success</v>
@@ -5434,7 +5434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F252" t="str">
         <v>Success</v>
@@ -5454,7 +5454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F253" t="str">
         <v>Success</v>
@@ -5474,7 +5474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F254" t="str">
         <v>Success</v>
@@ -5494,7 +5494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F255" t="str">
         <v>Success</v>
@@ -5514,7 +5514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F256" t="str">
         <v>Success</v>
@@ -5534,7 +5534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F257" t="str">
         <v>Success</v>
@@ -5554,7 +5554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F258" t="str">
         <v>Success</v>
@@ -5574,7 +5574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F259" t="str">
         <v>Success</v>
@@ -5594,7 +5594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F260" t="str">
         <v>Success</v>
@@ -5614,7 +5614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F261" t="str">
         <v>Success</v>
@@ -5634,7 +5634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F262" t="str">
         <v>Success</v>
@@ -5654,7 +5654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F263" t="str">
         <v>Success</v>
@@ -5674,7 +5674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F264" t="str">
         <v>Success</v>
@@ -5694,7 +5694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F265" t="str">
         <v>Success</v>
@@ -5714,7 +5714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F266" t="str">
         <v>Success</v>
@@ -5734,7 +5734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F267" t="str">
         <v>Success</v>
@@ -5754,7 +5754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F268" t="str">
         <v>Success</v>
@@ -5774,7 +5774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F269" t="str">
         <v>Success</v>
@@ -5794,7 +5794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F270" t="str">
         <v>Success</v>
@@ -5814,7 +5814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F271" t="str">
         <v>Success</v>
@@ -5834,7 +5834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F272" t="str">
         <v>Success</v>
@@ -5854,7 +5854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F273" t="str">
         <v>Success</v>
@@ -5874,7 +5874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F274" t="str">
         <v>Success</v>
@@ -5894,7 +5894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F275" t="str">
         <v>Success</v>
@@ -5914,7 +5914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F276" t="str">
         <v>Success</v>
@@ -5934,7 +5934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F277" t="str">
         <v>Success</v>
@@ -5954,7 +5954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F278" t="str">
         <v>Success</v>
@@ -5974,7 +5974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F279" t="str">
         <v>Success</v>
@@ -5994,7 +5994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F280" t="str">
         <v>Success</v>
@@ -6014,7 +6014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F281" t="str">
         <v>Success</v>
@@ -6034,7 +6034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F282" t="str">
         <v>Success</v>
@@ -6054,7 +6054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F283" t="str">
         <v>Success</v>
@@ -6074,7 +6074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F284" t="str">
         <v>Success</v>
@@ -6094,7 +6094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F285" t="str">
         <v>Success</v>
@@ -6114,7 +6114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F286" t="str">
         <v>Success</v>
@@ -6134,7 +6134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F287" t="str">
         <v>Success</v>
@@ -6154,7 +6154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F288" t="str">
         <v>Success</v>
@@ -6174,7 +6174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F289" t="str">
         <v>Success</v>
@@ -6194,7 +6194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F290" t="str">
         <v>Success</v>
@@ -6214,7 +6214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F291" t="str">
         <v>Success</v>
@@ -6234,7 +6234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F292" t="str">
         <v>Success</v>
@@ -6254,7 +6254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F293" t="str">
         <v>Success</v>
@@ -6274,7 +6274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F294" t="str">
         <v>Success</v>
@@ -6294,7 +6294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F295" t="str">
         <v>Success</v>
@@ -6314,7 +6314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F296" t="str">
         <v>Success</v>
@@ -6334,7 +6334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F297" t="str">
         <v>Success</v>
@@ -6354,7 +6354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F298" t="str">
         <v>Success</v>
@@ -6374,7 +6374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F299" t="str">
         <v>Success</v>
@@ -6394,7 +6394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F300" t="str">
         <v>Success</v>
@@ -6414,7 +6414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F301" t="str">
         <v>Success</v>
@@ -6434,7 +6434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F302" t="str">
         <v>Success</v>
@@ -6454,7 +6454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F303" t="str">
         <v>Success</v>
@@ -6474,7 +6474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F304" t="str">
         <v>Success</v>
@@ -6494,7 +6494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F305" t="str">
         <v>Success</v>
@@ -6514,7 +6514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F306" t="str">
         <v>Success</v>
@@ -6534,7 +6534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F307" t="str">
         <v>Success</v>
@@ -6554,7 +6554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F308" t="str">
         <v>Success</v>
@@ -6574,7 +6574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F309" t="str">
         <v>Success</v>
@@ -6594,7 +6594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F310" t="str">
         <v>Success</v>
@@ -6614,7 +6614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F311" t="str">
         <v>Success</v>
@@ -6634,7 +6634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F312" t="str">
         <v>Success</v>
@@ -6654,7 +6654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F313" t="str">
         <v>Success</v>
@@ -6674,7 +6674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F314" t="str">
         <v>Success</v>
@@ -6694,7 +6694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F315" t="str">
         <v>Success</v>
@@ -6714,7 +6714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F316" t="str">
         <v>Success</v>
@@ -6734,7 +6734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F317" t="str">
         <v>Success</v>
@@ -6754,7 +6754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F318" t="str">
         <v>Success</v>
@@ -6774,7 +6774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F319" t="str">
         <v>Success</v>
@@ -6794,7 +6794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F320" t="str">
         <v>Success</v>
@@ -6814,7 +6814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F321" t="str">
         <v>Success</v>
@@ -6834,7 +6834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F322" t="str">
         <v>Success</v>
@@ -6854,7 +6854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F323" t="str">
         <v>Success</v>
@@ -6874,7 +6874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F324" t="str">
         <v>Success</v>
@@ -6894,7 +6894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F325" t="str">
         <v>Success</v>
@@ -6914,7 +6914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F326" t="str">
         <v>Success</v>
@@ -6934,7 +6934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F327" t="str">
         <v>Success</v>
@@ -6954,7 +6954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F328" t="str">
         <v>Success</v>
@@ -6974,7 +6974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F329" t="str">
         <v>Success</v>
@@ -6994,7 +6994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F330" t="str">
         <v>Success</v>
@@ -7014,7 +7014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F331" t="str">
         <v>Success</v>
@@ -7034,7 +7034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F332" t="str">
         <v>Success</v>
@@ -7054,7 +7054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F333" t="str">
         <v>Success</v>
@@ -7074,7 +7074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F334" t="str">
         <v>Success</v>
@@ -7094,7 +7094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F335" t="str">
         <v>Success</v>
@@ -7114,7 +7114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F336" t="str">
         <v>Success</v>
@@ -7134,7 +7134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F337" t="str">
         <v>Success</v>
@@ -7154,7 +7154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F338" t="str">
         <v>Success</v>
@@ -7174,7 +7174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F339" t="str">
         <v>Success</v>
@@ -7194,7 +7194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F340" t="str">
         <v>Success</v>
@@ -7214,7 +7214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F341" t="str">
         <v>Success</v>
@@ -7234,7 +7234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F342" t="str">
         <v>Success</v>
@@ -7254,7 +7254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F343" t="str">
         <v>Success</v>
@@ -7274,7 +7274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F344" t="str">
         <v>Success</v>
@@ -7294,7 +7294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F345" t="str">
         <v>Success</v>
@@ -7314,7 +7314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F346" t="str">
         <v>Success</v>
@@ -7334,7 +7334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F347" t="str">
         <v>Success</v>
@@ -7354,7 +7354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F348" t="str">
         <v>Success</v>
@@ -7374,7 +7374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F349" t="str">
         <v>Success</v>
@@ -7394,7 +7394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F350" t="str">
         <v>Success</v>
@@ -7414,7 +7414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F351" t="str">
         <v>Success</v>
@@ -7434,7 +7434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F352" t="str">
         <v>Success</v>
@@ -7454,7 +7454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F353" t="str">
         <v>Success</v>
@@ -7474,7 +7474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F354" t="str">
         <v>Success</v>
@@ -7494,7 +7494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F355" t="str">
         <v>Success</v>
@@ -7514,7 +7514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F356" t="str">
         <v>Success</v>
@@ -7534,7 +7534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F357" t="str">
         <v>Success</v>
@@ -7554,7 +7554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F358" t="str">
         <v>Success</v>
@@ -7574,7 +7574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F359" t="str">
         <v>Success</v>
@@ -7594,7 +7594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F360" t="str">
         <v>Success</v>
@@ -7614,7 +7614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F361" t="str">
         <v>Success</v>
@@ -7634,7 +7634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F362" t="str">
         <v>Success</v>
@@ -7654,7 +7654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F363" t="str">
         <v>Success</v>
@@ -7674,7 +7674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F364" t="str">
         <v>Success</v>
@@ -7694,7 +7694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F365" t="str">
         <v>Success</v>
@@ -7714,7 +7714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F366" t="str">
         <v>Success</v>
@@ -7734,7 +7734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F367" t="str">
         <v>Success</v>
@@ -7754,7 +7754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F368" t="str">
         <v>Success</v>
@@ -7774,7 +7774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F369" t="str">
         <v>Success</v>
@@ -7794,7 +7794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F370" t="str">
         <v>Success</v>
@@ -7814,7 +7814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F371" t="str">
         <v>Success</v>
@@ -7834,7 +7834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F372" t="str">
         <v>Success</v>
@@ -7854,7 +7854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F373" t="str">
         <v>Success</v>
@@ -7874,7 +7874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F374" t="str">
         <v>Success</v>
@@ -7894,7 +7894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F375" t="str">
         <v>Success</v>
@@ -7914,7 +7914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F376" t="str">
         <v>Success</v>
@@ -7934,7 +7934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F377" t="str">
         <v>Success</v>
@@ -7954,7 +7954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F378" t="str">
         <v>Success</v>
@@ -7974,7 +7974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F379" t="str">
         <v>Success</v>
@@ -7994,7 +7994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F380" t="str">
         <v>Success</v>
@@ -8014,7 +8014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F381" t="str">
         <v>Success</v>
@@ -8034,7 +8034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F382" t="str">
         <v>Success</v>
@@ -8054,7 +8054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F383" t="str">
         <v>Success</v>
@@ -8074,7 +8074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F384" t="str">
         <v>Success</v>
@@ -8094,7 +8094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F385" t="str">
         <v>Success</v>
@@ -8114,7 +8114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F386" t="str">
         <v>Success</v>
@@ -8134,7 +8134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F387" t="str">
         <v>Success</v>
@@ -8154,7 +8154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F388" t="str">
         <v>Success</v>
@@ -8174,7 +8174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F389" t="str">
         <v>Success</v>
@@ -8194,7 +8194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F390" t="str">
         <v>Success</v>
@@ -8214,7 +8214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F391" t="str">
         <v>Success</v>
@@ -8234,7 +8234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F392" t="str">
         <v>Success</v>
@@ -8254,7 +8254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F393" t="str">
         <v>Success</v>
@@ -8274,7 +8274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F394" t="str">
         <v>Success</v>
@@ -8294,7 +8294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F395" t="str">
         <v>Success</v>
@@ -8314,7 +8314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F396" t="str">
         <v>Success</v>
@@ -8334,7 +8334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F397" t="str">
         <v>Success</v>
@@ -8354,7 +8354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F398" t="str">
         <v>Success</v>
@@ -8374,7 +8374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F399" t="str">
         <v>Success</v>
@@ -8394,7 +8394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F400" t="str">
         <v>Success</v>
@@ -8414,7 +8414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F401" t="str">
         <v>Success</v>
